--- a/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
+++ b/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
@@ -31856,24 +31856,26 @@
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="38" t="n">
-        <f>IF(OR(COUNTBLANK('Dimensions'!G56)&gt;0),"",'Dimensions'!G56)</f>
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="E38" s="39" t="n">
-        <f>IF(COUNTBLANK(D38)&gt;0,"",D38/1000)</f>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F38" s="18" t="inlineStr">
         <is>
-          <t>P049</t>
+          <t>P049 (PDF 750); DWG0378</t>
         </is>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
-          <t>Printed elevation</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="str"/>
+          <t>Owner direction 24 Oct 2026 · CAD file 23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>CAD sections 25 and 45 draw the dais at +0.800 (800 mm dimension, platform lines). The PDF set and the CAD ground-plan label give +0.750 (P049, ISSUE-R04). The model uses +0.800 by owner direction.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
@@ -31888,24 +31890,26 @@
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="38" t="n">
-        <f>IF(OR(COUNTBLANK('Dimensions'!G57)&gt;0),"",'Dimensions'!G57)</f>
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E39" s="39" t="n">
-        <f>IF(COUNTBLANK(D39)&gt;0,"",D39/1000)</f>
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F39" s="18" t="inlineStr">
         <is>
-          <t>P050</t>
+          <t>P050 (PDF 150); DWG0373</t>
         </is>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
-          <t>Printed elevation</t>
-        </is>
-      </c>
-      <c r="H39" s="18" t="str"/>
+          <t>Owner direction 24 Oct 2026 · CAD file 23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>CAD section 25 dimensions the side floor 160 mm. The PDF set and the CAD ground-plan labels give +0.150. The model uses +0.160 by owner direction.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
@@ -31952,24 +31956,26 @@
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="38" t="n">
-        <f>IF(OR(COUNTBLANK('Dimensions'!G59)&gt;0),"",'Dimensions'!G59)</f>
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E41" s="39" t="n">
-        <f>IF(COUNTBLANK(D41)&gt;0,"",D41/1000)</f>
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="F41" s="18" t="inlineStr">
         <is>
-          <t>P052</t>
+          <t>P052 (PDF 150); DWG0373</t>
         </is>
       </c>
       <c r="G41" s="18" t="inlineStr">
         <is>
-          <t>Printed elevation</t>
-        </is>
-      </c>
-      <c r="H41" s="18" t="str"/>
+          <t>Owner direction 24 Oct 2026 · CAD file 23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>CAD section 25 dimensions the side floor 160 mm. The PDF set and the CAD ground-plan labels give +0.150. The model uses +0.160 by owner direction.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="18" t="inlineStr">

--- a/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
+++ b/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
@@ -12,6 +12,7 @@
     <sheet name="DWG levels" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="DWG grid check" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="DWG findings" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="DWG facade" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -413,6 +414,27 @@
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="DwgFacade" displayName="DwgFacade" ref="A7:L42" headerRowCount="1">
+  <autoFilter ref="A7:L42"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Mã / ID"/>
+    <tableColumn id="2" name="Bộ phận / Element"/>
+    <tableColumn id="3" name="Bản vẽ / Drawing"/>
+    <tableColumn id="4" name="Loại / Kind"/>
+    <tableColumn id="5" name="p1"/>
+    <tableColumn id="6" name="p2"/>
+    <tableColumn id="7" name="p3"/>
+    <tableColumn id="8" name="p4"/>
+    <tableColumn id="9" name="Giá trị (mm) / Value"/>
+    <tableColumn id="10" name="Mô hình / Model (m)"/>
+    <tableColumn id="11" name="Cơ sở / Basis"/>
+    <tableColumn id="12" name="Ghi chú / Note"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ModelCoordinates" displayName="ModelCoordinates" ref="A7:H58" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A7:H58"/>
@@ -30584,6 +30606,1782 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF18324B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:L42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="70" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1"/>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>MẶT GIỮA HAI THÁP THEO FILE CAD / CENTRAL FACADE FROM THE CAD FILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1"/>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Mô hình theo file CAD từ +8,45 m (chủ đầu tư, 24/10/2026). p1–p4: đường, cung hoặc kích thước được kiểm bằng `extract_dwg_revision.py facade`. / The model follows the CAD file above +8.45 m (owner, 2026-10-24). p1–p4 give the line, arc or dimension checked by `extract_dwg_revision.py facade`; elevation u = Z, v = Y; plans u = Z, v = X (mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Mã / ID</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Bộ phận / Element</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Bản vẽ / Drawing</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Loại / Kind</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Giá trị (mm) / Value</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>Mô hình / Model (m)</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>Cơ sở / Basis</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>Ghi chú / Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Ground-storey cornice top over the side bays</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E8" s="38" t="n">
+        <v>8390</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>-7703</v>
+      </c>
+      <c r="G8" s="38" t="n">
+        <v>-3469</v>
+      </c>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="38" t="n">
+        <v>8390</v>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>8.390</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>Kept from the bundle's traced facade; also the +8.390 level label</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Central cornice corona underside</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E9" s="38" t="n">
+        <v>8605</v>
+      </c>
+      <c r="F9" s="38" t="n">
+        <v>-3499</v>
+      </c>
+      <c r="G9" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="38" t="n">
+        <v>8605</v>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>8.605</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>Dentils 8.42–8.52 and corona 8.605–8.773 over the main door</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Central cornice Greek-key frieze top / plinth base</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E10" s="38" t="n">
+        <v>9115</v>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>-7128</v>
+      </c>
+      <c r="G10" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="38" t="n">
+        <v>9115</v>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>9.115</t>
+        </is>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>Runs across the three bays</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Upper-storey plinth top (terrace)</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E11" s="38" t="n">
+        <v>9741</v>
+      </c>
+      <c r="F11" s="38" t="n">
+        <v>-7128</v>
+      </c>
+      <c r="G11" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="38" t="n">
+        <v>9741</v>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>9.741</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>Floor of the side niches and of the room behind the triple window</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Upper entablature underside</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>15333</v>
+      </c>
+      <c r="F12" s="38" t="n">
+        <v>-7763</v>
+      </c>
+      <c r="G12" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="38" t="n">
+        <v>15333</v>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>15.333</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>F06</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Upper entablature top</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E13" s="38" t="n">
+        <v>15840</v>
+      </c>
+      <c r="F13" s="38" t="n">
+        <v>-7128</v>
+      </c>
+      <c r="G13" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="38" t="n">
+        <v>15840</v>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>15.840</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>Also the +15.840 level label and plan PT15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>F07</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Central piers: chain across the D–E bay</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="n">
+        <v>5958.8</v>
+      </c>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="44" t="n">
+        <v>5958.8</v>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>±2.979 (centres), shafts ±2.544 to ±3.414</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>621 / 5958.8 / 621 dimension chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>F08</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Central great arch extrados</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E15" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="38" t="n">
+        <v>12677</v>
+      </c>
+      <c r="G15" s="38" t="n">
+        <v>2270</v>
+      </c>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="38" t="n">
+        <v>2270</v>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>r 2.270 about +12.677</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>Rings at r 2.070 and 2.200 drawn between</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>Central great arch intrados</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>12677</v>
+      </c>
+      <c r="G16" s="38" t="n">
+        <v>1960</v>
+      </c>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="38" t="n">
+        <v>1960</v>
+      </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>r 1.960</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>Tympanum face inside it</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Triple window outer lights</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E17" s="38" t="n">
+        <v>-1190</v>
+      </c>
+      <c r="F17" s="38" t="n">
+        <v>12241</v>
+      </c>
+      <c r="G17" s="38" t="n">
+        <v>430</v>
+      </c>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="38" t="n">
+        <v>430</v>
+      </c>
+      <c r="J17" s="18" t="inlineStr">
+        <is>
+          <t>centres ±1.190, r 0.430 about +12.241</t>
+        </is>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>Glazing r 0.375; rings to r 0.650</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Triple window centre light</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="38" t="n">
+        <v>12241</v>
+      </c>
+      <c r="G18" s="38" t="n">
+        <v>430</v>
+      </c>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="38" t="n">
+        <v>430</v>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>centre 0, r 0.430 about +12.241</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Triple window glazing edge and sill</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="E19" s="38" t="n">
+        <v>-1605</v>
+      </c>
+      <c r="F19" s="38" t="n">
+        <v>9984</v>
+      </c>
+      <c r="G19" s="38" t="n">
+        <v>12101</v>
+      </c>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="38" t="n">
+        <v>9984</v>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>sill +9.984</t>
+        </is>
+      </c>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>Lights 0.830 m wide between colonnettes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Side great arch extrados</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>-5350</v>
+      </c>
+      <c r="F20" s="38" t="n">
+        <v>12960</v>
+      </c>
+      <c r="G20" s="38" t="n">
+        <v>1936</v>
+      </c>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="38" t="n">
+        <v>1936</v>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>centre ±5.350, r 1.936 about +12.960</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>F14</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Side great arch intrados</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E21" s="38" t="n">
+        <v>-5350</v>
+      </c>
+      <c r="F21" s="38" t="n">
+        <v>12960</v>
+      </c>
+      <c r="G21" s="38" t="n">
+        <v>1626</v>
+      </c>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="38" t="n">
+        <v>1626</v>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>r 1.626</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>Legs run down to the plinth</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>F15</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Side niche (intrados)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E22" s="38" t="n">
+        <v>-5350</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>12308</v>
+      </c>
+      <c r="G22" s="38" t="n">
+        <v>599</v>
+      </c>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="38" t="n">
+        <v>599</v>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>r 0.599 about +12.308; crown +12.907</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>Pedestal top +10.391; statue of the owner on it</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>F16</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Side aedicule arch extrados</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E23" s="38" t="n">
+        <v>-5350</v>
+      </c>
+      <c r="F23" s="38" t="n">
+        <v>12308</v>
+      </c>
+      <c r="G23" s="38" t="n">
+        <v>986</v>
+      </c>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="38" t="n">
+        <v>986</v>
+      </c>
+      <c r="J23" s="18" t="inlineStr">
+        <is>
+          <t>r 0.986</t>
+        </is>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>Carved crest above to about +14.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>F17</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Central niche (intrados)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E24" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="38" t="n">
+        <v>18893</v>
+      </c>
+      <c r="G24" s="38" t="n">
+        <v>711</v>
+      </c>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="38" t="n">
+        <v>711</v>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>r 0.711 about +18.893; crown +19.604</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>Pedestal 15.997–16.683</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Central aedicule arch extrados</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E25" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="38" t="n">
+        <v>18893</v>
+      </c>
+      <c r="G25" s="38" t="n">
+        <v>1112</v>
+      </c>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="38" t="n">
+        <v>1112</v>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>r 1.112</t>
+        </is>
+      </c>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>F19</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Pediment raking cornice (lower edge)</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>seg</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="n">
+        <v>-1316.4</v>
+      </c>
+      <c r="F26" s="44" t="n">
+        <v>20420.7</v>
+      </c>
+      <c r="G26" s="44" t="n">
+        <v>-361.5</v>
+      </c>
+      <c r="H26" s="44" t="n">
+        <v>21068.7</v>
+      </c>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>(±1.316, +20.421) to (±0.362, +21.069)</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Scroll spur from the pier pinnacle to the aedicule pier</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E27" s="38" t="n">
+        <v>-3404</v>
+      </c>
+      <c r="F27" s="38" t="n">
+        <v>18866</v>
+      </c>
+      <c r="G27" s="38" t="n">
+        <v>1317</v>
+      </c>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="38" t="n">
+        <v>1317</v>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>centre ±3.404, +18.866; r 1.317–1.417</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>F21</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Disc under the cross</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E28" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="38" t="n">
+        <v>22921</v>
+      </c>
+      <c r="G28" s="38" t="n">
+        <v>213</v>
+      </c>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="38" t="n">
+        <v>213</v>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>r 0.213 about +22.921</t>
+        </is>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>F22</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Cross top</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>ymax</t>
+        </is>
+      </c>
+      <c r="E29" s="38" t="n">
+        <v>-800</v>
+      </c>
+      <c r="F29" s="38" t="n">
+        <v>800</v>
+      </c>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="38" t="n">
+        <v>24648</v>
+      </c>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>24.648</t>
+        </is>
+      </c>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L29" s="18" t="inlineStr">
+        <is>
+          <t>Highest point of the central facade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>F23</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>Central pier front at the plinth</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>PT10</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E30" s="38" t="n">
+        <v>1562</v>
+      </c>
+      <c r="F30" s="38" t="n">
+        <v>-3472</v>
+      </c>
+      <c r="G30" s="38" t="n">
+        <v>-2484</v>
+      </c>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="38" t="n">
+        <v>1562</v>
+      </c>
+      <c r="J30" s="18" t="inlineStr">
+        <is>
+          <t>X 1.562</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L30" s="18" t="inlineStr">
+        <is>
+          <t>Plan at +10.128 m; X from axis 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>F24</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>Central bay wall face</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>PT10</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E31" s="38" t="n">
+        <v>2936</v>
+      </c>
+      <c r="F31" s="38" t="n">
+        <v>-2544</v>
+      </c>
+      <c r="G31" s="38" t="n">
+        <v>-2270</v>
+      </c>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="38" t="n">
+        <v>2936</v>
+      </c>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t>X 2.936</t>
+        </is>
+      </c>
+      <c r="K31" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L31" s="18" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>F25</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Triple window plane</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>PT10</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E32" s="38" t="n">
+        <v>3556</v>
+      </c>
+      <c r="F32" s="38" t="n">
+        <v>-1620</v>
+      </c>
+      <c r="G32" s="38" t="n">
+        <v>-760</v>
+      </c>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="38" t="n">
+        <v>3556</v>
+      </c>
+      <c r="J32" s="18" t="inlineStr">
+        <is>
+          <t>X 3.556 (louvres)</t>
+        </is>
+      </c>
+      <c r="K32" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L32" s="18" t="inlineStr">
+        <is>
+          <t>Room behind from X 3.666 to 4.716</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>F26</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Side bay wall face</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>PT10</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E33" s="38" t="n">
+        <v>4017</v>
+      </c>
+      <c r="F33" s="38" t="n">
+        <v>-4364</v>
+      </c>
+      <c r="G33" s="38" t="n">
+        <v>-3724</v>
+      </c>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="38" t="n">
+        <v>4017</v>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>X 4.017</t>
+        </is>
+      </c>
+      <c r="K33" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L33" s="18" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>F27</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Side bay wall back</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>PT10</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E34" s="38" t="n">
+        <v>4936</v>
+      </c>
+      <c r="F34" s="38" t="n">
+        <v>-6975</v>
+      </c>
+      <c r="G34" s="38" t="n">
+        <v>-3724</v>
+      </c>
+      <c r="H34" s="18" t="n"/>
+      <c r="I34" s="38" t="n">
+        <v>4936</v>
+      </c>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t>X 4.936</t>
+        </is>
+      </c>
+      <c r="K34" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L34" s="18" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>F28</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Pinnacle pedestal front</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>PT15</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E35" s="38" t="n">
+        <v>2096</v>
+      </c>
+      <c r="F35" s="38" t="n">
+        <v>-3414</v>
+      </c>
+      <c r="G35" s="38" t="n">
+        <v>-2544</v>
+      </c>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="38" t="n">
+        <v>2096</v>
+      </c>
+      <c r="J35" s="18" t="inlineStr">
+        <is>
+          <t>X 2.096</t>
+        </is>
+      </c>
+      <c r="K35" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L35" s="18" t="inlineStr">
+        <is>
+          <t>Plan at +15.840 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>F29</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Aedicule pier front</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>PT15</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E36" s="38" t="n">
+        <v>3805</v>
+      </c>
+      <c r="F36" s="38" t="n">
+        <v>-1885</v>
+      </c>
+      <c r="G36" s="38" t="n">
+        <v>-1439</v>
+      </c>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="38" t="n">
+        <v>3805</v>
+      </c>
+      <c r="J36" s="18" t="inlineStr">
+        <is>
+          <t>X 3.805</t>
+        </is>
+      </c>
+      <c r="K36" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L36" s="18" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>F30</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>Central niche column front</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>PT15</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E37" s="38" t="n">
+        <v>3915</v>
+      </c>
+      <c r="F37" s="38" t="n">
+        <v>-1112</v>
+      </c>
+      <c r="G37" s="38" t="n">
+        <v>-906</v>
+      </c>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="38" t="n">
+        <v>3915</v>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>X 3.915</t>
+        </is>
+      </c>
+      <c r="K37" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L37" s="18" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>F31</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>Central niche (plan)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>PT15</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>arc</t>
+        </is>
+      </c>
+      <c r="E38" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="38" t="n">
+        <v>4225</v>
+      </c>
+      <c r="G38" s="38" t="n">
+        <v>711</v>
+      </c>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="38" t="n">
+        <v>711</v>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>centre X 4.225, r 0.711</t>
+        </is>
+      </c>
+      <c r="K38" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L38" s="18" t="inlineStr">
+        <is>
+          <t>Niche back X 4.936; aedicule back X 5.046</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>F32</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>Cresting balustrade front</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>PT15</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E39" s="38" t="n">
+        <v>3376</v>
+      </c>
+      <c r="F39" s="38" t="n">
+        <v>-7086</v>
+      </c>
+      <c r="G39" s="38" t="n">
+        <v>-3614</v>
+      </c>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="38" t="n">
+        <v>3376</v>
+      </c>
+      <c r="J39" s="18" t="inlineStr">
+        <is>
+          <t>X 3.376</t>
+        </is>
+      </c>
+      <c r="K39" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L39" s="18" t="inlineStr">
+        <is>
+          <t>Fleur-de-lis posts at 617 mm spacing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Side bays meet the towers</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="38" t="n">
+        <v>7128</v>
+      </c>
+      <c r="J40" s="18" t="inlineStr">
+        <is>
+          <t>±7.500</t>
+        </is>
+      </c>
+      <c r="K40" s="18" t="inlineStr">
+        <is>
+          <t>MODEL ADJUSTMENT</t>
+        </is>
+      </c>
+      <c r="L40" s="18" t="inlineStr">
+        <is>
+          <t>The drawing stops the side bays at ±7.128 against the tower pilasters; the model's towers stand back at about ±7.5, so the side-bay wall, plinth and entablature run on to meet them</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>Moulding profiles and carving</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="inlineStr"/>
+      <c r="K41" s="18" t="inlineStr">
+        <is>
+          <t>ILLUSTRATIVE</t>
+        </is>
+      </c>
+      <c r="L41" s="18" t="inlineStr">
+        <is>
+          <t>Profiles, relief depths, capitals, cresting and crests are generated shapes that follow the drawing's outlines, not construction details</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Statues in the niches</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="18" t="n"/>
+      <c r="H42" s="18" t="n"/>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="18" t="inlineStr"/>
+      <c r="K42" s="18" t="inlineStr">
+        <is>
+          <t>USER CONFIRMED / CONCEPT</t>
+        </is>
+      </c>
+      <c r="L42" s="18" t="inlineStr">
+        <is>
+          <t>The drawing shows empty niches with pedestals; the owner's three statues (9 Oct 2026) stand on the drawn pedestals</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -83343,7 +85141,7 @@
       <c r="E19" s="18" t="n"/>
       <c r="F19" s="18" t="inlineStr">
         <is>
-          <t>The model follows the PDF; see ISSUE-R02.</t>
+          <t>Owner direction 24 Oct 2026: the model follows the DWG above +8.45 m (facade.csv, docs/facade-model.md). ISSUE-R02 stays open for the church.</t>
         </is>
       </c>
     </row>

--- a/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
+++ b/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
@@ -35335,7 +35335,7 @@
       <c r="H29" s="42" t="n"/>
       <c r="I29" s="30" t="n"/>
     </row>
-    <row r="30" ht="24" customHeight="1">
+    <row r="30" ht="120" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
         <is>
           <t>ISSUE-R01</t>
@@ -35359,18 +35359,22 @@
       <c r="E30" s="41" t="n"/>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>Chưa xác nhận / Open</t>
+          <t xml:space="preserve">USER CONFIRMED - project design basis; construction issue remains ENGINEERING HOLD</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>Nhà thờ/kiến trúc sư xác nhận bộ nào hiện hành và các PDF in từ thời điểm nào của file. / Church and designer to confirm which set is current and when the PDFs were plotted from this file.</t>
+          <t xml:space="preserve">Owner direction, 26 October 2026: use the DWG saved 23 October 2026 as the project design standard. Retain older PDF evidence and unresolved internal conflicts. Responsible designer to issue coordinated construction drawings.</t>
         </is>
       </c>
       <c r="H30" s="42" t="n"/>
-      <c r="I30" s="30" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
+      <c r="I30" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner instruction in project chat, 2026-10-26; same DWG SHA-256 as source file 10 (sheets.json).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
           <t>ISSUE-R02</t>
@@ -35383,7 +35387,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>DWG sheet 1 (variant A cut through the nave roof, variant B full elevation) shows one pedimented arched niche with a cross, flanked by crested parapets with fleur-de-lis cresting, two smaller arched niches and a triple-arched window under a rose above the main door. PDF sheet 1 shows a taller screen of three pinnacled gables, which the current model follows. Tower geometry and the central 7,200 mm bay are the same.</t>
+          <t xml:space="preserve">DWG sheet 1 (variant A cut through the nave roof, variant B full elevation) shows one pedimented arched niche with a cross, flanked by crested parapets with fleur-de-lis cresting, two smaller arched niches and a triple-arched window under a rose above the main door. PDF sheet 1 shows a taller screen of three pinnacled gables, which the model followed before the DWG facade adoption on 24 October 2026. Tower geometry and the central 7,200 mm bay are the same.</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
@@ -36078,7 +36082,7 @@
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Nguồn: file CAD nhận 24/10/2026 (MẶT BẰNG NHÀ THỜ GIÁO XỨ THẠCH BI.dwg A.dwg, lưu lần cuối 2026-10-23). Chỉ đọc đối tượng DIMENSION và nhãn cao độ. / Source: CAD file received 2026-10-24. Only DIMENSION objects and level labels are read; the DWG carries fewer dimensions than the PDF set. Not for construction.</t>
+          <t xml:space="preserve">Owner confirmed 26 October 2026: DWG saved 23 October 2026 governs project design. Current filename: MẶT BẰNG NHÀ THỜ GIÁO XỨ THẠCH BI.dwg; byte-identical to source file 10. 726 dimension objects; 79 level labels. Older PDF witnesses and all unresolved engineering conflicts are retained. Not for construction.</t>
         </is>
       </c>
     </row>

--- a/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
+++ b/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
@@ -453,7 +453,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="OpenDimensions" displayName="OpenDimensions" ref="A7:I34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="OpenDimensions" displayName="OpenDimensions" ref="A7:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A7:I29"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Mã / ID"/>
@@ -34398,7 +34398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35520,8 +35520,47 @@
       <c r="H34" s="42" t="n"/>
       <c r="I34" s="30" t="n"/>
     </row>
+    <row r="35" ht="140" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISSUE-R06</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn vị hình học và đơn vị chèn trong DWG</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DWG gốc và DXF mới đều có INSUNITS=1 (inch, đơn vị chèn). Chuỗi trục 4500/7200 và các nhãn cao độ theo m phù hợp cách hiểu hình học mm của mô hình; đây là diễn giải từ bản vẽ, chưa phải xác nhận đơn vị của người thiết kế. Không tự nhân hoặc chia tọa độ theo 25,4.</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tệp CAD nguồn 10; 726 đối tượng kích thước; 137 mốc trục</t>
+        </is>
+      </c>
+      <c r="E35" s="41"/>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chưa xác nhận / ENGINEERING HOLD</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Người thiết kế mở DWG trong AutoCAD/ODA, xác nhận đơn vị hình học, tỷ lệ chèn, đơn vị ghi kích thước và phát hành hồ sơ thi công thống nhất.</t>
+        </is>
+      </c>
+      <c r="H35" s="42"/>
+      <c r="I35" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kiểm tra trực tiếp 26/10/2026; Autodesk INSUNITS; review/dwg-vietnamese-23102026/kiem-tra-so-lieu.json</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F8:F34">
+  <conditionalFormatting sqref="F8:F35">
     <cfRule type="containsText" priority="1" operator="containsText" dxfId="1" text="Open"/>
     <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" text="Assumption"/>
   </conditionalFormatting>
@@ -36082,7 +36121,7 @@
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner confirmed 26 October 2026: DWG saved 23 October 2026 governs project design. Current filename: MẶT BẰNG NHÀ THỜ GIÁO XỨ THẠCH BI.dwg; byte-identical to source file 10. 726 dimension objects; 79 level labels. Older PDF witnesses and all unresolved engineering conflicts are retained. Not for construction.</t>
+          <t xml:space="preserve">Phiên bản 23102026. 726 kích thước thuộc 27 bản vẽ. Đơn vị mm suy từ chuỗi kích thước và nhãn m; INSUNITS gốc = 1 (inch, đơn vị chèn). Cần người thiết kế xác nhận đơn vị. Số ghi lấy trực tiếp từ chữ số lưu trong CAD. Không dùng để thi công.</t>
         </is>
       </c>
     </row>
@@ -51838,8 +51877,8 @@
       <c r="E258" s="44" t="n">
         <v>2100.5</v>
       </c>
-      <c r="F258" s="38" t="n">
-        <v>2100</v>
+      <c r="F258" s="38">
+        <v>2101</v>
       </c>
       <c r="G258" s="18" t="inlineStr">
         <is>
@@ -53038,8 +53077,8 @@
       <c r="E279" s="44" t="n">
         <v>2130.5</v>
       </c>
-      <c r="F279" s="38" t="n">
-        <v>2130</v>
+      <c r="F279" s="38">
+        <v>2131</v>
       </c>
       <c r="G279" s="18" t="inlineStr">
         <is>
@@ -53958,8 +53997,8 @@
       <c r="E295" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F295" s="38" t="n">
-        <v>2950</v>
+      <c r="F295" s="38">
+        <v>2951</v>
       </c>
       <c r="G295" s="18" t="inlineStr">
         <is>
@@ -54018,8 +54057,8 @@
       <c r="E296" s="44" t="n">
         <v>2980.5</v>
       </c>
-      <c r="F296" s="38" t="n">
-        <v>2980</v>
+      <c r="F296" s="38">
+        <v>2981</v>
       </c>
       <c r="G296" s="18" t="inlineStr">
         <is>
@@ -54810,8 +54849,8 @@
       <c r="E310" s="44" t="n">
         <v>2860.5</v>
       </c>
-      <c r="F310" s="38" t="n">
-        <v>2860</v>
+      <c r="F310" s="38">
+        <v>2861</v>
       </c>
       <c r="G310" s="18" t="inlineStr">
         <is>
@@ -55750,8 +55789,8 @@
       <c r="E326" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F326" s="38" t="n">
-        <v>2950</v>
+      <c r="F326" s="38">
+        <v>2951</v>
       </c>
       <c r="G326" s="18" t="inlineStr">
         <is>
@@ -56398,8 +56437,8 @@
       <c r="E337" s="44" t="n">
         <v>2300.5</v>
       </c>
-      <c r="F337" s="38" t="n">
-        <v>2300</v>
+      <c r="F337" s="38">
+        <v>2301</v>
       </c>
       <c r="G337" s="18" t="inlineStr">
         <is>
@@ -58398,8 +58437,8 @@
       <c r="E371" s="44" t="n">
         <v>3100.5</v>
       </c>
-      <c r="F371" s="38" t="n">
-        <v>3100</v>
+      <c r="F371" s="38">
+        <v>3101</v>
       </c>
       <c r="G371" s="18" t="inlineStr">
         <is>
@@ -58458,8 +58497,8 @@
       <c r="E372" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F372" s="38" t="n">
-        <v>2950</v>
+      <c r="F372" s="38">
+        <v>2951</v>
       </c>
       <c r="G372" s="18" t="inlineStr">
         <is>
@@ -58630,8 +58669,8 @@
       <c r="E375" s="44" t="n">
         <v>2300.5</v>
       </c>
-      <c r="F375" s="38" t="n">
-        <v>2300</v>
+      <c r="F375" s="38">
+        <v>2301</v>
       </c>
       <c r="G375" s="18" t="inlineStr">
         <is>
@@ -59366,8 +59405,8 @@
       <c r="E388" s="44" t="n">
         <v>3170.5</v>
       </c>
-      <c r="F388" s="38" t="n">
-        <v>3170</v>
+      <c r="F388" s="38">
+        <v>3171</v>
       </c>
       <c r="G388" s="18" t="inlineStr">
         <is>
@@ -62130,8 +62169,8 @@
       <c r="E437" s="44" t="n">
         <v>2130.5</v>
       </c>
-      <c r="F437" s="38" t="n">
-        <v>2130</v>
+      <c r="F437" s="38">
+        <v>2131</v>
       </c>
       <c r="G437" s="18" t="inlineStr">
         <is>
@@ -64138,8 +64177,8 @@
       <c r="E472" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F472" s="38" t="n">
-        <v>2950</v>
+      <c r="F472" s="38">
+        <v>2951</v>
       </c>
       <c r="G472" s="18" t="inlineStr">
         <is>
@@ -64194,8 +64233,8 @@
       <c r="E473" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F473" s="38" t="n">
-        <v>2950</v>
+      <c r="F473" s="38">
+        <v>2951</v>
       </c>
       <c r="G473" s="18" t="inlineStr">
         <is>
@@ -65722,8 +65761,8 @@
       <c r="E500" s="44" t="n">
         <v>2860.5</v>
       </c>
-      <c r="F500" s="38" t="n">
-        <v>2860</v>
+      <c r="F500" s="38">
+        <v>2861</v>
       </c>
       <c r="G500" s="18" t="inlineStr">
         <is>
@@ -67358,8 +67397,8 @@
       <c r="E529" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F529" s="38" t="n">
-        <v>2950</v>
+      <c r="F529" s="38">
+        <v>2951</v>
       </c>
       <c r="G529" s="18" t="inlineStr">
         <is>
@@ -67418,8 +67457,8 @@
       <c r="E530" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F530" s="38" t="n">
-        <v>2950</v>
+      <c r="F530" s="38">
+        <v>2951</v>
       </c>
       <c r="G530" s="18" t="inlineStr">
         <is>
@@ -69618,8 +69657,8 @@
       <c r="E569" s="44" t="n">
         <v>2440.5</v>
       </c>
-      <c r="F569" s="38" t="n">
-        <v>2440</v>
+      <c r="F569" s="38">
+        <v>2441</v>
       </c>
       <c r="G569" s="18" t="inlineStr">
         <is>
@@ -70130,8 +70169,8 @@
       <c r="E578" s="44" t="n">
         <v>2100.5</v>
       </c>
-      <c r="F578" s="38" t="n">
-        <v>2100</v>
+      <c r="F578" s="38">
+        <v>2101</v>
       </c>
       <c r="G578" s="18" t="inlineStr">
         <is>
@@ -70694,8 +70733,8 @@
       <c r="E588" s="44" t="n">
         <v>2440.5</v>
       </c>
-      <c r="F588" s="38" t="n">
-        <v>2440</v>
+      <c r="F588" s="38">
+        <v>2441</v>
       </c>
       <c r="G588" s="18" t="inlineStr">
         <is>
@@ -73622,8 +73661,8 @@
       <c r="E640" s="44" t="n">
         <v>2110.5</v>
       </c>
-      <c r="F640" s="38" t="n">
-        <v>2110</v>
+      <c r="F640" s="38">
+        <v>2111</v>
       </c>
       <c r="G640" s="18" t="inlineStr">
         <is>
@@ -75310,8 +75349,8 @@
       <c r="E670" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F670" s="38" t="n">
-        <v>2950</v>
+      <c r="F670" s="38">
+        <v>2951</v>
       </c>
       <c r="G670" s="18" t="inlineStr">
         <is>
@@ -75878,8 +75917,8 @@
       <c r="E680" s="44" t="n">
         <v>75.5</v>
       </c>
-      <c r="F680" s="38" t="n">
-        <v>75</v>
+      <c r="F680" s="38">
+        <v>76</v>
       </c>
       <c r="G680" s="18" t="inlineStr">
         <is>

--- a/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
+++ b/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
@@ -32284,17 +32284,17 @@
       </c>
       <c r="J40" s="18" t="inlineStr">
         <is>
-          <t>±7.500</t>
+          <t xml:space="preserve">±7.128</t>
         </is>
       </c>
       <c r="K40" s="18" t="inlineStr">
         <is>
-          <t>MODEL ADJUSTMENT</t>
+          <t xml:space="preserve">MODEL TRANSCRIPTION / COORDINATED</t>
         </is>
       </c>
       <c r="L40" s="18" t="inlineStr">
         <is>
-          <t>The drawing stops the side bays at ±7.128 against the tower pilasters; the model's towers stand back at about ±7.5, so the side-bay wall, plinth and entablature run on to meet them</t>
+          <t xml:space="preserve">26 Oct 2026: removed the former model extension to ±7.500 m. CAD stops at ±7.128 m; rebuilt tower rear piers start at ±7.103 m, giving 25 mm overlap. Source dimensions unchanged; structure/detail remain held.</t>
         </is>
       </c>
     </row>

--- a/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
+++ b/docs/layout_design/Thach_Bi_Church_Dimensions.xlsx
@@ -415,8 +415,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="DwgFacade" displayName="DwgFacade" ref="A7:L42" headerRowCount="1">
-  <autoFilter ref="A7:L42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="DwgFacade" displayName="DwgFacade" ref="A7:L45" headerRowCount="1">
+  <autoFilter ref="A7:L45"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Mã / ID"/>
     <tableColumn id="2" name="Bộ phận / Element"/>
@@ -30613,7 +30613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L42"/>
+  <dimension ref="A2:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -32257,118 +32257,268 @@
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>F33</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Side bays meet the towers</t>
+          <t>Tower front column base: height from the nave floor to the top of the base</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>E01B</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
-      <c r="G40" s="18" t="n"/>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="E40" s="38" t="n">
+        <v>12603</v>
+      </c>
+      <c r="F40" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="38" t="n">
+        <v>1848</v>
+      </c>
       <c r="H40" s="18" t="n"/>
       <c r="I40" s="38" t="n">
-        <v>7128</v>
+        <v>1848</v>
       </c>
       <c r="J40" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">±7.128</t>
+          <t>1.848</t>
         </is>
       </c>
       <c r="K40" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MODEL TRANSCRIPTION / COORDINATED</t>
+          <t>TRACED</t>
         </is>
       </c>
       <c r="L40" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">26 Oct 2026: removed the former model extension to ±7.500 m. CAD stops at ±7.128 m; rebuilt tower rear piers start at ±7.103 m, giving 25 mm overlap. Source dimensions unchanged; structure/detail remain held.</t>
+          <t>Column axis line at Z 12.603 checked from +0.000 to +1.848; top band line at +1.848 (Z 12.078–13.348) where the fluted shaft starts. The same +1.848 line is drawn on all four tower front columns (Z ±6.958–8.228 and ±12.078–13.348). Not a CAD dimension: read from the drawn lines</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>F34</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Moulding profiles and carving</t>
+          <t>Tower front column base: top of the middle mouldings</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>E01B</t>
         </is>
       </c>
       <c r="D41" s="18" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E41" s="38" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F41" s="38" t="n">
+        <v>12603</v>
+      </c>
+      <c r="G41" s="38" t="n">
+        <v>13366</v>
+      </c>
       <c r="H41" s="18" t="n"/>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="18" t="inlineStr"/>
+      <c r="I41" s="38" t="n">
+        <v>1368</v>
+      </c>
+      <c r="J41" s="18" t="inlineStr">
+        <is>
+          <t>1.368</t>
+        </is>
+      </c>
       <c r="K41" s="18" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE</t>
+          <t>TRACED</t>
         </is>
       </c>
       <c r="L41" s="18" t="inlineStr">
         <is>
-          <t>Profiles, relief depths, capitals, cresting and crests are generated shapes that follow the drawing's outlines, not construction details</t>
+          <t>Moulding top line; the moulded band runs from +1.032 to +1.368</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
+          <t>F35</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Tower front column base: top of the lowest block</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>E01B</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E42" s="38" t="n">
+        <v>443</v>
+      </c>
+      <c r="F42" s="38" t="n">
+        <v>12603</v>
+      </c>
+      <c r="G42" s="38" t="n">
+        <v>13414</v>
+      </c>
+      <c r="H42" s="18" t="n"/>
+      <c r="I42" s="38" t="n">
+        <v>443</v>
+      </c>
+      <c r="J42" s="18" t="inlineStr">
+        <is>
+          <t>0.443</t>
+        </is>
+      </c>
+      <c r="K42" s="18" t="inlineStr">
+        <is>
+          <t>TRACED</t>
+        </is>
+      </c>
+      <c r="L42" s="18" t="inlineStr">
+        <is>
+          <t>Top of the plinth block; mouldings from +0.215 below it</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Side bays meet the towers</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="n"/>
+      <c r="I43" s="38" t="n">
+        <v>7128</v>
+      </c>
+      <c r="J43" s="18" t="inlineStr">
+        <is>
+          <t>±7.128</t>
+        </is>
+      </c>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>MODEL TRANSCRIPTION / COORDINATED</t>
+        </is>
+      </c>
+      <c r="L43" s="18" t="inlineStr">
+        <is>
+          <t>26 Oct 2026: removed the former model extension to ±7.500 m. CAD stops at ±7.128 m; rebuilt tower rear piers start at ±7.103 m, giving 25 mm overlap. Source dimensions unchanged; structure/detail remain held.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Moulding profiles and carving</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="18" t="n"/>
+      <c r="I44" s="18" t="n"/>
+      <c r="J44" s="18" t="inlineStr"/>
+      <c r="K44" s="18" t="inlineStr">
+        <is>
+          <t>ILLUSTRATIVE</t>
+        </is>
+      </c>
+      <c r="L44" s="18" t="inlineStr">
+        <is>
+          <t>Profiles, relief depths, capitals, cresting and crests are generated shapes that follow the drawing's outlines, not construction details</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
           <t>D03</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>Statues in the niches</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D45" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E42" s="18" t="n"/>
-      <c r="F42" s="18" t="n"/>
-      <c r="G42" s="18" t="n"/>
-      <c r="H42" s="18" t="n"/>
-      <c r="I42" s="18" t="n"/>
-      <c r="J42" s="18" t="inlineStr"/>
-      <c r="K42" s="18" t="inlineStr">
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="n"/>
+      <c r="I45" s="18" t="n"/>
+      <c r="J45" s="18" t="inlineStr"/>
+      <c r="K45" s="18" t="inlineStr">
         <is>
           <t>USER CONFIRMED / CONCEPT</t>
         </is>
       </c>
-      <c r="L42" s="18" t="inlineStr">
+      <c r="L45" s="18" t="inlineStr">
         <is>
           <t>The drawing shows empty niches with pedestals; the owner's three statues (9 Oct 2026) stand on the drawn pedestals</t>
         </is>
@@ -35359,18 +35509,18 @@
       <c r="E30" s="41" t="n"/>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">USER CONFIRMED - project design basis; construction issue remains ENGINEERING HOLD</t>
+          <t>USER CONFIRMED - project design basis; construction issue remains ENGINEERING HOLD</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner direction, 26 October 2026: use the DWG saved 23 October 2026 as the project design standard. Retain older PDF evidence and unresolved internal conflicts. Responsible designer to issue coordinated construction drawings.</t>
+          <t>Owner direction, 26 October 2026: use the DWG saved 23 October 2026 as the project design standard. Retain older PDF evidence and unresolved internal conflicts. Responsible designer to issue coordinated construction drawings.</t>
         </is>
       </c>
       <c r="H30" s="42" t="n"/>
       <c r="I30" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner instruction in project chat, 2026-10-26; same DWG SHA-256 as source file 10 (sheets.json).</t>
+          <t>Owner instruction in project chat, 2026-10-26; same DWG SHA-256 as source file 10 (sheets.json).</t>
         </is>
       </c>
     </row>
@@ -35387,7 +35537,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DWG sheet 1 (variant A cut through the nave roof, variant B full elevation) shows one pedimented arched niche with a cross, flanked by crested parapets with fleur-de-lis cresting, two smaller arched niches and a triple-arched window under a rose above the main door. PDF sheet 1 shows a taller screen of three pinnacled gables, which the model followed before the DWG facade adoption on 24 October 2026. Tower geometry and the central 7,200 mm bay are the same.</t>
+          <t>DWG sheet 1 (variant A cut through the nave roof, variant B full elevation) shows one pedimented arched niche with a cross, flanked by crested parapets with fleur-de-lis cresting, two smaller arched niches and a triple-arched window under a rose above the main door. PDF sheet 1 shows a taller screen of three pinnacled gables, which the model followed before the DWG facade adoption on 24 October 2026. Tower geometry and the central 7,200 mm bay are the same.</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
@@ -35523,39 +35673,39 @@
     <row r="35" ht="140" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISSUE-R06</t>
+          <t>ISSUE-R06</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đơn vị hình học và đơn vị chèn trong DWG</t>
+          <t>Đơn vị hình học và đơn vị chèn trong DWG</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DWG gốc và DXF mới đều có INSUNITS=1 (inch, đơn vị chèn). Chuỗi trục 4500/7200 và các nhãn cao độ theo m phù hợp cách hiểu hình học mm của mô hình; đây là diễn giải từ bản vẽ, chưa phải xác nhận đơn vị của người thiết kế. Không tự nhân hoặc chia tọa độ theo 25,4.</t>
+          <t>DWG gốc và DXF mới đều có INSUNITS=1 (inch, đơn vị chèn). Chuỗi trục 4500/7200 và các nhãn cao độ theo m phù hợp cách hiểu hình học mm của mô hình; đây là diễn giải từ bản vẽ, chưa phải xác nhận đơn vị của người thiết kế. Không tự nhân hoặc chia tọa độ theo 25,4.</t>
         </is>
       </c>
       <c r="D35" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tệp CAD nguồn 10; 726 đối tượng kích thước; 137 mốc trục</t>
-        </is>
-      </c>
-      <c r="E35" s="41"/>
+          <t>Tệp CAD nguồn 10; 726 đối tượng kích thước; 137 mốc trục</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="n"/>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chưa xác nhận / ENGINEERING HOLD</t>
+          <t>Chưa xác nhận / ENGINEERING HOLD</t>
         </is>
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Người thiết kế mở DWG trong AutoCAD/ODA, xác nhận đơn vị hình học, tỷ lệ chèn, đơn vị ghi kích thước và phát hành hồ sơ thi công thống nhất.</t>
-        </is>
-      </c>
-      <c r="H35" s="42"/>
+          <t>Người thiết kế mở DWG trong AutoCAD/ODA, xác nhận đơn vị hình học, tỷ lệ chèn, đơn vị ghi kích thước và phát hành hồ sơ thi công thống nhất.</t>
+        </is>
+      </c>
+      <c r="H35" s="42" t="n"/>
       <c r="I35" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kiểm tra trực tiếp 26/10/2026; Autodesk INSUNITS; review/dwg-vietnamese-23102026/kiem-tra-so-lieu.json</t>
+          <t>Kiểm tra trực tiếp 26/10/2026; Autodesk INSUNITS; review/dwg-vietnamese-23102026/kiem-tra-so-lieu.json</t>
         </is>
       </c>
     </row>
@@ -36121,7 +36271,7 @@
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phiên bản 23102026. 726 kích thước thuộc 27 bản vẽ. Đơn vị mm suy từ chuỗi kích thước và nhãn m; INSUNITS gốc = 1 (inch, đơn vị chèn). Cần người thiết kế xác nhận đơn vị. Số ghi lấy trực tiếp từ chữ số lưu trong CAD. Không dùng để thi công.</t>
+          <t>Phiên bản 23102026. 726 kích thước thuộc 27 bản vẽ. Đơn vị mm suy từ chuỗi kích thước và nhãn m; INSUNITS gốc = 1 (inch, đơn vị chèn). Cần người thiết kế xác nhận đơn vị. Số ghi lấy trực tiếp từ chữ số lưu trong CAD. Không dùng để thi công.</t>
         </is>
       </c>
     </row>
@@ -51877,7 +52027,7 @@
       <c r="E258" s="44" t="n">
         <v>2100.5</v>
       </c>
-      <c r="F258" s="38">
+      <c r="F258" s="38" t="n">
         <v>2101</v>
       </c>
       <c r="G258" s="18" t="inlineStr">
@@ -53077,7 +53227,7 @@
       <c r="E279" s="44" t="n">
         <v>2130.5</v>
       </c>
-      <c r="F279" s="38">
+      <c r="F279" s="38" t="n">
         <v>2131</v>
       </c>
       <c r="G279" s="18" t="inlineStr">
@@ -53997,7 +54147,7 @@
       <c r="E295" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F295" s="38">
+      <c r="F295" s="38" t="n">
         <v>2951</v>
       </c>
       <c r="G295" s="18" t="inlineStr">
@@ -54057,7 +54207,7 @@
       <c r="E296" s="44" t="n">
         <v>2980.5</v>
       </c>
-      <c r="F296" s="38">
+      <c r="F296" s="38" t="n">
         <v>2981</v>
       </c>
       <c r="G296" s="18" t="inlineStr">
@@ -54849,7 +54999,7 @@
       <c r="E310" s="44" t="n">
         <v>2860.5</v>
       </c>
-      <c r="F310" s="38">
+      <c r="F310" s="38" t="n">
         <v>2861</v>
       </c>
       <c r="G310" s="18" t="inlineStr">
@@ -55789,7 +55939,7 @@
       <c r="E326" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F326" s="38">
+      <c r="F326" s="38" t="n">
         <v>2951</v>
       </c>
       <c r="G326" s="18" t="inlineStr">
@@ -56437,7 +56587,7 @@
       <c r="E337" s="44" t="n">
         <v>2300.5</v>
       </c>
-      <c r="F337" s="38">
+      <c r="F337" s="38" t="n">
         <v>2301</v>
       </c>
       <c r="G337" s="18" t="inlineStr">
@@ -58437,7 +58587,7 @@
       <c r="E371" s="44" t="n">
         <v>3100.5</v>
       </c>
-      <c r="F371" s="38">
+      <c r="F371" s="38" t="n">
         <v>3101</v>
       </c>
       <c r="G371" s="18" t="inlineStr">
@@ -58497,7 +58647,7 @@
       <c r="E372" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F372" s="38">
+      <c r="F372" s="38" t="n">
         <v>2951</v>
       </c>
       <c r="G372" s="18" t="inlineStr">
@@ -58669,7 +58819,7 @@
       <c r="E375" s="44" t="n">
         <v>2300.5</v>
       </c>
-      <c r="F375" s="38">
+      <c r="F375" s="38" t="n">
         <v>2301</v>
       </c>
       <c r="G375" s="18" t="inlineStr">
@@ -59405,7 +59555,7 @@
       <c r="E388" s="44" t="n">
         <v>3170.5</v>
       </c>
-      <c r="F388" s="38">
+      <c r="F388" s="38" t="n">
         <v>3171</v>
       </c>
       <c r="G388" s="18" t="inlineStr">
@@ -62169,7 +62319,7 @@
       <c r="E437" s="44" t="n">
         <v>2130.5</v>
       </c>
-      <c r="F437" s="38">
+      <c r="F437" s="38" t="n">
         <v>2131</v>
       </c>
       <c r="G437" s="18" t="inlineStr">
@@ -64177,7 +64327,7 @@
       <c r="E472" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F472" s="38">
+      <c r="F472" s="38" t="n">
         <v>2951</v>
       </c>
       <c r="G472" s="18" t="inlineStr">
@@ -64233,7 +64383,7 @@
       <c r="E473" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F473" s="38">
+      <c r="F473" s="38" t="n">
         <v>2951</v>
       </c>
       <c r="G473" s="18" t="inlineStr">
@@ -65761,7 +65911,7 @@
       <c r="E500" s="44" t="n">
         <v>2860.5</v>
       </c>
-      <c r="F500" s="38">
+      <c r="F500" s="38" t="n">
         <v>2861</v>
       </c>
       <c r="G500" s="18" t="inlineStr">
@@ -67397,7 +67547,7 @@
       <c r="E529" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F529" s="38">
+      <c r="F529" s="38" t="n">
         <v>2951</v>
       </c>
       <c r="G529" s="18" t="inlineStr">
@@ -67457,7 +67607,7 @@
       <c r="E530" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F530" s="38">
+      <c r="F530" s="38" t="n">
         <v>2951</v>
       </c>
       <c r="G530" s="18" t="inlineStr">
@@ -69657,7 +69807,7 @@
       <c r="E569" s="44" t="n">
         <v>2440.5</v>
       </c>
-      <c r="F569" s="38">
+      <c r="F569" s="38" t="n">
         <v>2441</v>
       </c>
       <c r="G569" s="18" t="inlineStr">
@@ -70169,7 +70319,7 @@
       <c r="E578" s="44" t="n">
         <v>2100.5</v>
       </c>
-      <c r="F578" s="38">
+      <c r="F578" s="38" t="n">
         <v>2101</v>
       </c>
       <c r="G578" s="18" t="inlineStr">
@@ -70733,7 +70883,7 @@
       <c r="E588" s="44" t="n">
         <v>2440.5</v>
       </c>
-      <c r="F588" s="38">
+      <c r="F588" s="38" t="n">
         <v>2441</v>
       </c>
       <c r="G588" s="18" t="inlineStr">
@@ -73661,7 +73811,7 @@
       <c r="E640" s="44" t="n">
         <v>2110.5</v>
       </c>
-      <c r="F640" s="38">
+      <c r="F640" s="38" t="n">
         <v>2111</v>
       </c>
       <c r="G640" s="18" t="inlineStr">
@@ -75349,7 +75499,7 @@
       <c r="E670" s="44" t="n">
         <v>2950.5</v>
       </c>
-      <c r="F670" s="38">
+      <c r="F670" s="38" t="n">
         <v>2951</v>
       </c>
       <c r="G670" s="18" t="inlineStr">
@@ -75917,7 +76067,7 @@
       <c r="E680" s="44" t="n">
         <v>75.5</v>
       </c>
-      <c r="F680" s="38">
+      <c r="F680" s="38" t="n">
         <v>76</v>
       </c>
       <c r="G680" s="18" t="inlineStr">
